--- a/bs_optimization/output/swap_on_stochastic_notional.xlsx
+++ b/bs_optimization/output/swap_on_stochastic_notional.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E133"/>
+  <dimension ref="A1:E85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -450,2509 +450,1597 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>LADDER_5Y_E000</t>
+          <t>LADDER_7Y_E000</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C2" t="n">
         <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>153295.258023646</v>
+        <v>133853.9569212658</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>45657</v>
+        <v>46203</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>LADDER_5Y_E001</t>
+          <t>LADDER_7Y_E001</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C3" t="n">
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>153295.258023646</v>
+        <v>133853.9569212658</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>45626</v>
+        <v>46172</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>LADDER_5Y_E002</t>
+          <t>LADDER_7Y_E002</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C4" t="n">
         <v>2</v>
       </c>
       <c r="D4" t="n">
-        <v>153295.258023646</v>
+        <v>133853.9569212658</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>45596</v>
+        <v>46142</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>LADDER_5Y_E003</t>
+          <t>LADDER_7Y_E003</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C5" t="n">
         <v>3</v>
       </c>
       <c r="D5" t="n">
-        <v>153295.258023646</v>
+        <v>133853.9569212658</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>45565</v>
+        <v>46111</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>LADDER_5Y_E004</t>
+          <t>LADDER_7Y_E004</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C6" t="n">
         <v>4</v>
       </c>
       <c r="D6" t="n">
-        <v>153295.258023646</v>
+        <v>133853.9569212658</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>45535</v>
+        <v>46081</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>LADDER_5Y_E005</t>
+          <t>LADDER_7Y_E005</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C7" t="n">
         <v>5</v>
       </c>
       <c r="D7" t="n">
-        <v>153295.258023646</v>
+        <v>133853.9569212658</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>45504</v>
+        <v>46052</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>LADDER_5Y_E006</t>
+          <t>LADDER_7Y_E006</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C8" t="n">
         <v>6</v>
       </c>
       <c r="D8" t="n">
-        <v>153295.258023646</v>
+        <v>133853.9569212658</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>45473</v>
+        <v>46021</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>LADDER_5Y_E007</t>
+          <t>LADDER_7Y_E007</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C9" t="n">
         <v>7</v>
       </c>
       <c r="D9" t="n">
-        <v>153295.258023646</v>
+        <v>133853.9569212658</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>45443</v>
+        <v>45991</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>LADDER_5Y_E008</t>
+          <t>LADDER_7Y_E008</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C10" t="n">
         <v>8</v>
       </c>
       <c r="D10" t="n">
-        <v>153295.258023646</v>
+        <v>133853.9569212658</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>45412</v>
+        <v>45960</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>LADDER_5Y_E009</t>
+          <t>LADDER_7Y_E009</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C11" t="n">
         <v>9</v>
       </c>
       <c r="D11" t="n">
-        <v>153295.258023646</v>
+        <v>133853.9569212658</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>45382</v>
+        <v>45930</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>LADDER_5Y_E010</t>
+          <t>LADDER_7Y_E010</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C12" t="n">
         <v>10</v>
       </c>
       <c r="D12" t="n">
-        <v>153295.258023646</v>
+        <v>133853.9569212658</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>45351</v>
+        <v>45899</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>LADDER_5Y_E011</t>
+          <t>LADDER_7Y_E011</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C13" t="n">
         <v>11</v>
       </c>
       <c r="D13" t="n">
-        <v>153295.258023646</v>
+        <v>133853.9569212658</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>45322</v>
+        <v>45868</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>LADDER_5Y_E012</t>
+          <t>LADDER_7Y_E012</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C14" t="n">
         <v>12</v>
       </c>
       <c r="D14" t="n">
-        <v>153295.258023646</v>
+        <v>133853.9569212658</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>45291</v>
+        <v>45838</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>LADDER_5Y_E013</t>
+          <t>LADDER_7Y_E013</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C15" t="n">
         <v>13</v>
       </c>
       <c r="D15" t="n">
-        <v>153295.258023646</v>
+        <v>133853.9569212658</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>45260</v>
+        <v>45807</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>LADDER_5Y_E014</t>
+          <t>LADDER_7Y_E014</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C16" t="n">
         <v>14</v>
       </c>
       <c r="D16" t="n">
-        <v>153295.258023646</v>
+        <v>133853.9569212658</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>45230</v>
+        <v>45777</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>LADDER_5Y_E015</t>
+          <t>LADDER_7Y_E015</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C17" t="n">
         <v>15</v>
       </c>
       <c r="D17" t="n">
-        <v>153295.258023646</v>
+        <v>133853.9569212658</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>45199</v>
+        <v>45746</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>LADDER_5Y_E016</t>
+          <t>LADDER_7Y_E016</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C18" t="n">
         <v>16</v>
       </c>
       <c r="D18" t="n">
-        <v>153295.258023646</v>
+        <v>133853.9569212658</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>45169</v>
+        <v>45716</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>LADDER_5Y_E017</t>
+          <t>LADDER_7Y_E017</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C19" t="n">
         <v>17</v>
       </c>
       <c r="D19" t="n">
-        <v>153295.258023646</v>
+        <v>133853.9569212658</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>45138</v>
+        <v>45687</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>LADDER_5Y_E018</t>
+          <t>LADDER_7Y_E018</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C20" t="n">
         <v>18</v>
       </c>
       <c r="D20" t="n">
-        <v>153295.258023646</v>
+        <v>133853.9569212658</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>45107</v>
+        <v>45656</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>LADDER_5Y_E019</t>
+          <t>LADDER_7Y_E019</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C21" t="n">
         <v>19</v>
       </c>
       <c r="D21" t="n">
-        <v>153295.258023646</v>
+        <v>133853.9569212658</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>45077</v>
+        <v>45626</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>LADDER_5Y_E020</t>
+          <t>LADDER_7Y_E020</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C22" t="n">
         <v>20</v>
       </c>
       <c r="D22" t="n">
-        <v>153295.258023646</v>
+        <v>133853.9569212658</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>45046</v>
+        <v>45595</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>LADDER_5Y_E021</t>
+          <t>LADDER_7Y_E021</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C23" t="n">
         <v>21</v>
       </c>
       <c r="D23" t="n">
-        <v>153295.258023646</v>
+        <v>133853.9569212658</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>45016</v>
+        <v>45565</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>LADDER_5Y_E022</t>
+          <t>LADDER_7Y_E022</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C24" t="n">
         <v>22</v>
       </c>
       <c r="D24" t="n">
-        <v>153295.258023646</v>
+        <v>133853.9569212658</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>44985</v>
+        <v>45534</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>LADDER_5Y_E023</t>
+          <t>LADDER_7Y_E023</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C25" t="n">
         <v>23</v>
       </c>
       <c r="D25" t="n">
-        <v>153295.258023646</v>
+        <v>133853.9569212658</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>44957</v>
+        <v>45503</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>LADDER_5Y_E024</t>
+          <t>LADDER_7Y_E024</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C26" t="n">
         <v>24</v>
       </c>
       <c r="D26" t="n">
-        <v>153295.258023646</v>
+        <v>133853.9569212658</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>44926</v>
+        <v>45473</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>LADDER_5Y_E025</t>
+          <t>LADDER_7Y_E025</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C27" t="n">
         <v>25</v>
       </c>
       <c r="D27" t="n">
-        <v>153295.258023646</v>
+        <v>133853.9569212658</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>44895</v>
+        <v>45442</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>LADDER_5Y_E026</t>
+          <t>LADDER_7Y_E026</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C28" t="n">
         <v>26</v>
       </c>
       <c r="D28" t="n">
-        <v>153295.258023646</v>
+        <v>133853.9569212658</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>44865</v>
+        <v>45412</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>LADDER_5Y_E027</t>
+          <t>LADDER_7Y_E027</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C29" t="n">
         <v>27</v>
       </c>
       <c r="D29" t="n">
-        <v>153295.258023646</v>
+        <v>133853.9569212658</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>44834</v>
+        <v>45381</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>LADDER_5Y_E028</t>
+          <t>LADDER_7Y_E028</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C30" t="n">
         <v>28</v>
       </c>
       <c r="D30" t="n">
-        <v>153295.258023646</v>
+        <v>133853.9569212658</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>44804</v>
+        <v>45351</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>LADDER_5Y_E029</t>
+          <t>LADDER_7Y_E029</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C31" t="n">
         <v>29</v>
       </c>
       <c r="D31" t="n">
-        <v>153295.258023646</v>
+        <v>133853.9569212658</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>44773</v>
+        <v>45321</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>LADDER_5Y_E030</t>
+          <t>LADDER_7Y_E030</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C32" t="n">
         <v>30</v>
       </c>
       <c r="D32" t="n">
-        <v>153295.258023646</v>
+        <v>133853.9569212658</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>44742</v>
+        <v>45290</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>LADDER_5Y_E031</t>
+          <t>LADDER_7Y_E031</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C33" t="n">
         <v>31</v>
       </c>
       <c r="D33" t="n">
-        <v>153295.258023646</v>
+        <v>133853.9569212658</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>44712</v>
+        <v>45260</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>LADDER_5Y_E032</t>
+          <t>LADDER_7Y_E032</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C34" t="n">
         <v>32</v>
       </c>
       <c r="D34" t="n">
-        <v>153295.258023646</v>
+        <v>133853.9569212658</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>44681</v>
+        <v>45229</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>LADDER_5Y_E033</t>
+          <t>LADDER_7Y_E033</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C35" t="n">
         <v>33</v>
       </c>
       <c r="D35" t="n">
-        <v>153295.258023646</v>
+        <v>133853.9569212658</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>44651</v>
+        <v>45199</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>LADDER_5Y_E034</t>
+          <t>LADDER_7Y_E034</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C36" t="n">
         <v>34</v>
       </c>
       <c r="D36" t="n">
-        <v>153295.258023646</v>
+        <v>133853.9569212658</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>44620</v>
+        <v>45168</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>LADDER_5Y_E035</t>
+          <t>LADDER_7Y_E035</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C37" t="n">
         <v>35</v>
       </c>
       <c r="D37" t="n">
-        <v>153295.258023646</v>
+        <v>133853.9569212658</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>44592</v>
+        <v>45137</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>LADDER_5Y_E036</t>
+          <t>LADDER_7Y_E036</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C38" t="n">
         <v>36</v>
       </c>
       <c r="D38" t="n">
-        <v>153295.258023646</v>
+        <v>133853.9569212658</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>44561</v>
+        <v>45107</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>LADDER_5Y_E037</t>
+          <t>LADDER_7Y_E037</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C39" t="n">
         <v>37</v>
       </c>
       <c r="D39" t="n">
-        <v>153295.258023646</v>
+        <v>133853.9569212658</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>44530</v>
+        <v>45076</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>LADDER_5Y_E038</t>
+          <t>LADDER_7Y_E038</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C40" t="n">
         <v>38</v>
       </c>
       <c r="D40" t="n">
-        <v>153295.258023646</v>
+        <v>133853.9569212658</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>44500</v>
+        <v>45046</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>LADDER_5Y_E039</t>
+          <t>LADDER_7Y_E039</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C41" t="n">
         <v>39</v>
       </c>
       <c r="D41" t="n">
-        <v>153295.258023646</v>
+        <v>133853.9569212658</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>44469</v>
+        <v>45015</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>LADDER_5Y_E040</t>
+          <t>LADDER_7Y_E040</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C42" t="n">
         <v>40</v>
       </c>
       <c r="D42" t="n">
-        <v>153295.258023646</v>
+        <v>133853.9569212658</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>44439</v>
+        <v>44985</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>LADDER_5Y_E041</t>
+          <t>LADDER_7Y_E041</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C43" t="n">
         <v>41</v>
       </c>
       <c r="D43" t="n">
-        <v>153295.258023646</v>
+        <v>133853.9569212658</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>44408</v>
+        <v>44956</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>LADDER_5Y_E042</t>
+          <t>LADDER_7Y_E042</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C44" t="n">
         <v>42</v>
       </c>
       <c r="D44" t="n">
-        <v>153295.258023646</v>
+        <v>133853.9569212658</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>44377</v>
+        <v>44925</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>LADDER_5Y_E043</t>
+          <t>LADDER_7Y_E043</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C45" t="n">
         <v>43</v>
       </c>
       <c r="D45" t="n">
-        <v>153295.258023646</v>
+        <v>133853.9569212658</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>44347</v>
+        <v>44895</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>LADDER_5Y_E044</t>
+          <t>LADDER_7Y_E044</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C46" t="n">
         <v>44</v>
       </c>
       <c r="D46" t="n">
-        <v>153295.258023646</v>
+        <v>133853.9569212658</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>44316</v>
+        <v>44864</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>LADDER_5Y_E045</t>
+          <t>LADDER_7Y_E045</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C47" t="n">
         <v>45</v>
       </c>
       <c r="D47" t="n">
-        <v>153295.258023646</v>
+        <v>133853.9569212658</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>44286</v>
+        <v>44834</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>LADDER_5Y_E046</t>
+          <t>LADDER_7Y_E046</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C48" t="n">
         <v>46</v>
       </c>
       <c r="D48" t="n">
-        <v>153295.258023646</v>
+        <v>133853.9569212658</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>44255</v>
+        <v>44803</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>LADDER_5Y_E047</t>
+          <t>LADDER_7Y_E047</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C49" t="n">
         <v>47</v>
       </c>
       <c r="D49" t="n">
-        <v>153295.258023646</v>
+        <v>133853.9569212658</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>44227</v>
+        <v>44772</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>LADDER_5Y_E048</t>
+          <t>LADDER_7Y_E048</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C50" t="n">
         <v>48</v>
       </c>
       <c r="D50" t="n">
-        <v>153295.258023646</v>
+        <v>133853.9569212658</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>44196</v>
+        <v>44742</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>LADDER_5Y_E049</t>
+          <t>LADDER_7Y_E049</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C51" t="n">
         <v>49</v>
       </c>
       <c r="D51" t="n">
-        <v>153295.258023646</v>
+        <v>133853.9569212658</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>44165</v>
+        <v>44711</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>LADDER_5Y_E050</t>
+          <t>LADDER_7Y_E050</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C52" t="n">
         <v>50</v>
       </c>
       <c r="D52" t="n">
-        <v>153295.258023646</v>
+        <v>133853.9569212658</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>44135</v>
+        <v>44681</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>LADDER_5Y_E051</t>
+          <t>LADDER_7Y_E051</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C53" t="n">
         <v>51</v>
       </c>
       <c r="D53" t="n">
-        <v>153295.258023646</v>
+        <v>133853.9569212658</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>44104</v>
+        <v>44650</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>LADDER_5Y_E052</t>
+          <t>LADDER_7Y_E052</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C54" t="n">
         <v>52</v>
       </c>
       <c r="D54" t="n">
-        <v>153295.258023646</v>
+        <v>133853.9569212658</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>44074</v>
+        <v>44620</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>LADDER_5Y_E053</t>
+          <t>LADDER_7Y_E053</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C55" t="n">
         <v>53</v>
       </c>
       <c r="D55" t="n">
-        <v>153295.258023646</v>
+        <v>133853.9569212658</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>44043</v>
+        <v>44591</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>LADDER_5Y_E054</t>
+          <t>LADDER_7Y_E054</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C56" t="n">
         <v>54</v>
       </c>
       <c r="D56" t="n">
-        <v>153295.258023646</v>
+        <v>133853.9569212658</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>44012</v>
+        <v>44560</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>LADDER_5Y_E055</t>
+          <t>LADDER_7Y_E055</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C57" t="n">
         <v>55</v>
       </c>
       <c r="D57" t="n">
-        <v>153295.258023646</v>
+        <v>133853.9569212658</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>43982</v>
+        <v>44530</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>LADDER_5Y_E056</t>
+          <t>LADDER_7Y_E056</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C58" t="n">
         <v>56</v>
       </c>
       <c r="D58" t="n">
-        <v>153295.258023646</v>
+        <v>133853.9569212658</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>43951</v>
+        <v>44499</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>LADDER_5Y_E057</t>
+          <t>LADDER_7Y_E057</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C59" t="n">
         <v>57</v>
       </c>
       <c r="D59" t="n">
-        <v>153295.258023646</v>
+        <v>133853.9569212658</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>43921</v>
+        <v>44469</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>LADDER_5Y_E058</t>
+          <t>LADDER_7Y_E058</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C60" t="n">
         <v>58</v>
       </c>
       <c r="D60" t="n">
-        <v>153295.258023646</v>
+        <v>133853.9569212658</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>43890</v>
+        <v>44438</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>LADDER_5Y_E059</t>
+          <t>LADDER_7Y_E059</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C61" t="n">
         <v>59</v>
       </c>
       <c r="D61" t="n">
-        <v>153295.258023646</v>
+        <v>133853.9569212658</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>43861</v>
+        <v>44407</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>LADDER_6Y_E000</t>
+          <t>LADDER_7Y_E060</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C62" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="D62" t="n">
-        <v>3868192.416318498</v>
+        <v>133853.9569212658</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>45657</v>
+        <v>44377</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>LADDER_6Y_E001</t>
+          <t>LADDER_7Y_E061</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C63" t="n">
-        <v>1</v>
+        <v>61</v>
       </c>
       <c r="D63" t="n">
-        <v>3868192.416318498</v>
+        <v>133853.9569212658</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>45626</v>
+        <v>44346</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>LADDER_6Y_E002</t>
+          <t>LADDER_7Y_E062</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C64" t="n">
-        <v>2</v>
+        <v>62</v>
       </c>
       <c r="D64" t="n">
-        <v>3868192.416318498</v>
+        <v>133853.9569212658</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>45596</v>
+        <v>44316</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>LADDER_6Y_E003</t>
+          <t>LADDER_7Y_E063</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C65" t="n">
-        <v>3</v>
+        <v>63</v>
       </c>
       <c r="D65" t="n">
-        <v>3868192.416318498</v>
+        <v>133853.9569212658</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>45565</v>
+        <v>44285</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>LADDER_6Y_E004</t>
+          <t>LADDER_7Y_E064</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C66" t="n">
-        <v>4</v>
+        <v>64</v>
       </c>
       <c r="D66" t="n">
-        <v>3868192.416318498</v>
+        <v>133853.9569212658</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>45535</v>
+        <v>44255</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>LADDER_6Y_E005</t>
+          <t>LADDER_7Y_E065</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C67" t="n">
-        <v>5</v>
+        <v>65</v>
       </c>
       <c r="D67" t="n">
-        <v>3868192.416318498</v>
+        <v>133853.9569212658</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>45504</v>
+        <v>44226</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>LADDER_6Y_E006</t>
+          <t>LADDER_7Y_E066</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C68" t="n">
-        <v>6</v>
+        <v>66</v>
       </c>
       <c r="D68" t="n">
-        <v>3868192.416318498</v>
+        <v>133853.9569212658</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>45473</v>
+        <v>44195</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>LADDER_6Y_E007</t>
+          <t>LADDER_7Y_E067</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C69" t="n">
-        <v>7</v>
+        <v>67</v>
       </c>
       <c r="D69" t="n">
-        <v>3868192.416318498</v>
+        <v>133853.9569212658</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>45443</v>
+        <v>44165</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>LADDER_6Y_E008</t>
+          <t>LADDER_7Y_E068</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C70" t="n">
-        <v>8</v>
+        <v>68</v>
       </c>
       <c r="D70" t="n">
-        <v>3868192.416318498</v>
+        <v>133853.9569212658</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>45412</v>
+        <v>44134</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>LADDER_6Y_E009</t>
+          <t>LADDER_7Y_E069</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C71" t="n">
-        <v>9</v>
+        <v>69</v>
       </c>
       <c r="D71" t="n">
-        <v>3868192.416318498</v>
+        <v>133853.9569212658</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>45382</v>
+        <v>44104</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>LADDER_6Y_E010</t>
+          <t>LADDER_7Y_E070</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C72" t="n">
-        <v>10</v>
+        <v>70</v>
       </c>
       <c r="D72" t="n">
-        <v>3868192.416318498</v>
+        <v>133853.9569212658</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>45351</v>
+        <v>44073</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>LADDER_6Y_E011</t>
+          <t>LADDER_7Y_E071</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C73" t="n">
-        <v>11</v>
+        <v>71</v>
       </c>
       <c r="D73" t="n">
-        <v>3868192.416318498</v>
+        <v>133853.9569212658</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>45322</v>
+        <v>44042</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>LADDER_6Y_E012</t>
+          <t>LADDER_7Y_E072</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C74" t="n">
-        <v>12</v>
+        <v>72</v>
       </c>
       <c r="D74" t="n">
-        <v>3868192.416318498</v>
+        <v>133853.9569212658</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>45291</v>
+        <v>44012</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>LADDER_6Y_E013</t>
+          <t>LADDER_7Y_E073</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C75" t="n">
-        <v>13</v>
+        <v>73</v>
       </c>
       <c r="D75" t="n">
-        <v>3868192.416318498</v>
+        <v>133853.9569212658</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>45260</v>
+        <v>43981</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>LADDER_6Y_E014</t>
+          <t>LADDER_7Y_E074</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C76" t="n">
-        <v>14</v>
+        <v>74</v>
       </c>
       <c r="D76" t="n">
-        <v>3868192.416318498</v>
+        <v>133853.9569212658</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>45230</v>
+        <v>43951</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>LADDER_6Y_E015</t>
+          <t>LADDER_7Y_E075</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C77" t="n">
-        <v>15</v>
+        <v>75</v>
       </c>
       <c r="D77" t="n">
-        <v>3868192.416318498</v>
+        <v>133853.9569212658</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>45199</v>
+        <v>43920</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>LADDER_6Y_E016</t>
+          <t>LADDER_7Y_E076</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C78" t="n">
-        <v>16</v>
+        <v>76</v>
       </c>
       <c r="D78" t="n">
-        <v>3868192.416318498</v>
+        <v>133853.9569212658</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>45169</v>
+        <v>43890</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>LADDER_6Y_E017</t>
+          <t>LADDER_7Y_E077</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C79" t="n">
-        <v>17</v>
+        <v>77</v>
       </c>
       <c r="D79" t="n">
-        <v>3868192.416318498</v>
+        <v>133853.9569212658</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>45138</v>
+        <v>43860</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>LADDER_6Y_E018</t>
+          <t>LADDER_7Y_E078</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C80" t="n">
-        <v>18</v>
+        <v>78</v>
       </c>
       <c r="D80" t="n">
-        <v>3868192.416318498</v>
+        <v>133853.9569212658</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>45107</v>
+        <v>43829</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>LADDER_6Y_E019</t>
+          <t>LADDER_7Y_E079</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C81" t="n">
-        <v>19</v>
+        <v>79</v>
       </c>
       <c r="D81" t="n">
-        <v>3868192.416318498</v>
+        <v>133853.9569212658</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>45077</v>
+        <v>43799</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>LADDER_6Y_E020</t>
+          <t>LADDER_7Y_E080</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C82" t="n">
-        <v>20</v>
+        <v>80</v>
       </c>
       <c r="D82" t="n">
-        <v>3868192.416318498</v>
+        <v>133853.9569212658</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>45046</v>
+        <v>43768</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>LADDER_6Y_E021</t>
+          <t>LADDER_7Y_E081</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C83" t="n">
-        <v>21</v>
+        <v>81</v>
       </c>
       <c r="D83" t="n">
-        <v>3868192.416318498</v>
+        <v>133853.9569212658</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>45016</v>
+        <v>43738</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>LADDER_6Y_E022</t>
+          <t>LADDER_7Y_E082</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C84" t="n">
-        <v>22</v>
+        <v>82</v>
       </c>
       <c r="D84" t="n">
-        <v>3868192.416318498</v>
+        <v>133853.9569212658</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>44985</v>
+        <v>43707</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>LADDER_6Y_E023</t>
+          <t>LADDER_7Y_E083</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C85" t="n">
-        <v>23</v>
+        <v>83</v>
       </c>
       <c r="D85" t="n">
-        <v>3868192.416318498</v>
+        <v>133853.9569212658</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>44957</v>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>LADDER_6Y_E024</t>
-        </is>
-      </c>
-      <c r="B86" t="n">
-        <v>6</v>
-      </c>
-      <c r="C86" t="n">
-        <v>24</v>
-      </c>
-      <c r="D86" t="n">
-        <v>3868192.416318498</v>
-      </c>
-      <c r="E86" s="1" t="n">
-        <v>44926</v>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>LADDER_6Y_E025</t>
-        </is>
-      </c>
-      <c r="B87" t="n">
-        <v>6</v>
-      </c>
-      <c r="C87" t="n">
-        <v>25</v>
-      </c>
-      <c r="D87" t="n">
-        <v>3868192.416318498</v>
-      </c>
-      <c r="E87" s="1" t="n">
-        <v>44895</v>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>LADDER_6Y_E026</t>
-        </is>
-      </c>
-      <c r="B88" t="n">
-        <v>6</v>
-      </c>
-      <c r="C88" t="n">
-        <v>26</v>
-      </c>
-      <c r="D88" t="n">
-        <v>3868192.416318498</v>
-      </c>
-      <c r="E88" s="1" t="n">
-        <v>44865</v>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>LADDER_6Y_E027</t>
-        </is>
-      </c>
-      <c r="B89" t="n">
-        <v>6</v>
-      </c>
-      <c r="C89" t="n">
-        <v>27</v>
-      </c>
-      <c r="D89" t="n">
-        <v>3868192.416318498</v>
-      </c>
-      <c r="E89" s="1" t="n">
-        <v>44834</v>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>LADDER_6Y_E028</t>
-        </is>
-      </c>
-      <c r="B90" t="n">
-        <v>6</v>
-      </c>
-      <c r="C90" t="n">
-        <v>28</v>
-      </c>
-      <c r="D90" t="n">
-        <v>3868192.416318498</v>
-      </c>
-      <c r="E90" s="1" t="n">
-        <v>44804</v>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>LADDER_6Y_E029</t>
-        </is>
-      </c>
-      <c r="B91" t="n">
-        <v>6</v>
-      </c>
-      <c r="C91" t="n">
-        <v>29</v>
-      </c>
-      <c r="D91" t="n">
-        <v>3868192.416318498</v>
-      </c>
-      <c r="E91" s="1" t="n">
-        <v>44773</v>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>LADDER_6Y_E030</t>
-        </is>
-      </c>
-      <c r="B92" t="n">
-        <v>6</v>
-      </c>
-      <c r="C92" t="n">
-        <v>30</v>
-      </c>
-      <c r="D92" t="n">
-        <v>3868192.416318498</v>
-      </c>
-      <c r="E92" s="1" t="n">
-        <v>44742</v>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>LADDER_6Y_E031</t>
-        </is>
-      </c>
-      <c r="B93" t="n">
-        <v>6</v>
-      </c>
-      <c r="C93" t="n">
-        <v>31</v>
-      </c>
-      <c r="D93" t="n">
-        <v>3868192.416318498</v>
-      </c>
-      <c r="E93" s="1" t="n">
-        <v>44712</v>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>LADDER_6Y_E032</t>
-        </is>
-      </c>
-      <c r="B94" t="n">
-        <v>6</v>
-      </c>
-      <c r="C94" t="n">
-        <v>32</v>
-      </c>
-      <c r="D94" t="n">
-        <v>3868192.416318498</v>
-      </c>
-      <c r="E94" s="1" t="n">
-        <v>44681</v>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>LADDER_6Y_E033</t>
-        </is>
-      </c>
-      <c r="B95" t="n">
-        <v>6</v>
-      </c>
-      <c r="C95" t="n">
-        <v>33</v>
-      </c>
-      <c r="D95" t="n">
-        <v>3868192.416318498</v>
-      </c>
-      <c r="E95" s="1" t="n">
-        <v>44651</v>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>LADDER_6Y_E034</t>
-        </is>
-      </c>
-      <c r="B96" t="n">
-        <v>6</v>
-      </c>
-      <c r="C96" t="n">
-        <v>34</v>
-      </c>
-      <c r="D96" t="n">
-        <v>3868192.416318498</v>
-      </c>
-      <c r="E96" s="1" t="n">
-        <v>44620</v>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>LADDER_6Y_E035</t>
-        </is>
-      </c>
-      <c r="B97" t="n">
-        <v>6</v>
-      </c>
-      <c r="C97" t="n">
-        <v>35</v>
-      </c>
-      <c r="D97" t="n">
-        <v>3868192.416318498</v>
-      </c>
-      <c r="E97" s="1" t="n">
-        <v>44592</v>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>LADDER_6Y_E036</t>
-        </is>
-      </c>
-      <c r="B98" t="n">
-        <v>6</v>
-      </c>
-      <c r="C98" t="n">
-        <v>36</v>
-      </c>
-      <c r="D98" t="n">
-        <v>3868192.416318498</v>
-      </c>
-      <c r="E98" s="1" t="n">
-        <v>44561</v>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>LADDER_6Y_E037</t>
-        </is>
-      </c>
-      <c r="B99" t="n">
-        <v>6</v>
-      </c>
-      <c r="C99" t="n">
-        <v>37</v>
-      </c>
-      <c r="D99" t="n">
-        <v>3868192.416318498</v>
-      </c>
-      <c r="E99" s="1" t="n">
-        <v>44530</v>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>LADDER_6Y_E038</t>
-        </is>
-      </c>
-      <c r="B100" t="n">
-        <v>6</v>
-      </c>
-      <c r="C100" t="n">
-        <v>38</v>
-      </c>
-      <c r="D100" t="n">
-        <v>3868192.416318498</v>
-      </c>
-      <c r="E100" s="1" t="n">
-        <v>44500</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>LADDER_6Y_E039</t>
-        </is>
-      </c>
-      <c r="B101" t="n">
-        <v>6</v>
-      </c>
-      <c r="C101" t="n">
-        <v>39</v>
-      </c>
-      <c r="D101" t="n">
-        <v>3868192.416318498</v>
-      </c>
-      <c r="E101" s="1" t="n">
-        <v>44469</v>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="inlineStr">
-        <is>
-          <t>LADDER_6Y_E040</t>
-        </is>
-      </c>
-      <c r="B102" t="n">
-        <v>6</v>
-      </c>
-      <c r="C102" t="n">
-        <v>40</v>
-      </c>
-      <c r="D102" t="n">
-        <v>3868192.416318498</v>
-      </c>
-      <c r="E102" s="1" t="n">
-        <v>44439</v>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="inlineStr">
-        <is>
-          <t>LADDER_6Y_E041</t>
-        </is>
-      </c>
-      <c r="B103" t="n">
-        <v>6</v>
-      </c>
-      <c r="C103" t="n">
-        <v>41</v>
-      </c>
-      <c r="D103" t="n">
-        <v>3868192.416318498</v>
-      </c>
-      <c r="E103" s="1" t="n">
-        <v>44408</v>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="inlineStr">
-        <is>
-          <t>LADDER_6Y_E042</t>
-        </is>
-      </c>
-      <c r="B104" t="n">
-        <v>6</v>
-      </c>
-      <c r="C104" t="n">
-        <v>42</v>
-      </c>
-      <c r="D104" t="n">
-        <v>3868192.416318498</v>
-      </c>
-      <c r="E104" s="1" t="n">
-        <v>44377</v>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="inlineStr">
-        <is>
-          <t>LADDER_6Y_E043</t>
-        </is>
-      </c>
-      <c r="B105" t="n">
-        <v>6</v>
-      </c>
-      <c r="C105" t="n">
-        <v>43</v>
-      </c>
-      <c r="D105" t="n">
-        <v>3868192.416318498</v>
-      </c>
-      <c r="E105" s="1" t="n">
-        <v>44347</v>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" t="inlineStr">
-        <is>
-          <t>LADDER_6Y_E044</t>
-        </is>
-      </c>
-      <c r="B106" t="n">
-        <v>6</v>
-      </c>
-      <c r="C106" t="n">
-        <v>44</v>
-      </c>
-      <c r="D106" t="n">
-        <v>3868192.416318498</v>
-      </c>
-      <c r="E106" s="1" t="n">
-        <v>44316</v>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" t="inlineStr">
-        <is>
-          <t>LADDER_6Y_E045</t>
-        </is>
-      </c>
-      <c r="B107" t="n">
-        <v>6</v>
-      </c>
-      <c r="C107" t="n">
-        <v>45</v>
-      </c>
-      <c r="D107" t="n">
-        <v>3868192.416318498</v>
-      </c>
-      <c r="E107" s="1" t="n">
-        <v>44286</v>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" t="inlineStr">
-        <is>
-          <t>LADDER_6Y_E046</t>
-        </is>
-      </c>
-      <c r="B108" t="n">
-        <v>6</v>
-      </c>
-      <c r="C108" t="n">
-        <v>46</v>
-      </c>
-      <c r="D108" t="n">
-        <v>3868192.416318498</v>
-      </c>
-      <c r="E108" s="1" t="n">
-        <v>44255</v>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" t="inlineStr">
-        <is>
-          <t>LADDER_6Y_E047</t>
-        </is>
-      </c>
-      <c r="B109" t="n">
-        <v>6</v>
-      </c>
-      <c r="C109" t="n">
-        <v>47</v>
-      </c>
-      <c r="D109" t="n">
-        <v>3868192.416318498</v>
-      </c>
-      <c r="E109" s="1" t="n">
-        <v>44227</v>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" t="inlineStr">
-        <is>
-          <t>LADDER_6Y_E048</t>
-        </is>
-      </c>
-      <c r="B110" t="n">
-        <v>6</v>
-      </c>
-      <c r="C110" t="n">
-        <v>48</v>
-      </c>
-      <c r="D110" t="n">
-        <v>3868192.416318498</v>
-      </c>
-      <c r="E110" s="1" t="n">
-        <v>44196</v>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" t="inlineStr">
-        <is>
-          <t>LADDER_6Y_E049</t>
-        </is>
-      </c>
-      <c r="B111" t="n">
-        <v>6</v>
-      </c>
-      <c r="C111" t="n">
-        <v>49</v>
-      </c>
-      <c r="D111" t="n">
-        <v>3868192.416318498</v>
-      </c>
-      <c r="E111" s="1" t="n">
-        <v>44165</v>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" t="inlineStr">
-        <is>
-          <t>LADDER_6Y_E050</t>
-        </is>
-      </c>
-      <c r="B112" t="n">
-        <v>6</v>
-      </c>
-      <c r="C112" t="n">
-        <v>50</v>
-      </c>
-      <c r="D112" t="n">
-        <v>3868192.416318498</v>
-      </c>
-      <c r="E112" s="1" t="n">
-        <v>44135</v>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" t="inlineStr">
-        <is>
-          <t>LADDER_6Y_E051</t>
-        </is>
-      </c>
-      <c r="B113" t="n">
-        <v>6</v>
-      </c>
-      <c r="C113" t="n">
-        <v>51</v>
-      </c>
-      <c r="D113" t="n">
-        <v>3868192.416318498</v>
-      </c>
-      <c r="E113" s="1" t="n">
-        <v>44104</v>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" t="inlineStr">
-        <is>
-          <t>LADDER_6Y_E052</t>
-        </is>
-      </c>
-      <c r="B114" t="n">
-        <v>6</v>
-      </c>
-      <c r="C114" t="n">
-        <v>52</v>
-      </c>
-      <c r="D114" t="n">
-        <v>3868192.416318498</v>
-      </c>
-      <c r="E114" s="1" t="n">
-        <v>44074</v>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" t="inlineStr">
-        <is>
-          <t>LADDER_6Y_E053</t>
-        </is>
-      </c>
-      <c r="B115" t="n">
-        <v>6</v>
-      </c>
-      <c r="C115" t="n">
-        <v>53</v>
-      </c>
-      <c r="D115" t="n">
-        <v>3868192.416318498</v>
-      </c>
-      <c r="E115" s="1" t="n">
-        <v>44043</v>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" t="inlineStr">
-        <is>
-          <t>LADDER_6Y_E054</t>
-        </is>
-      </c>
-      <c r="B116" t="n">
-        <v>6</v>
-      </c>
-      <c r="C116" t="n">
-        <v>54</v>
-      </c>
-      <c r="D116" t="n">
-        <v>3868192.416318498</v>
-      </c>
-      <c r="E116" s="1" t="n">
-        <v>44012</v>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" t="inlineStr">
-        <is>
-          <t>LADDER_6Y_E055</t>
-        </is>
-      </c>
-      <c r="B117" t="n">
-        <v>6</v>
-      </c>
-      <c r="C117" t="n">
-        <v>55</v>
-      </c>
-      <c r="D117" t="n">
-        <v>3868192.416318498</v>
-      </c>
-      <c r="E117" s="1" t="n">
-        <v>43982</v>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" t="inlineStr">
-        <is>
-          <t>LADDER_6Y_E056</t>
-        </is>
-      </c>
-      <c r="B118" t="n">
-        <v>6</v>
-      </c>
-      <c r="C118" t="n">
-        <v>56</v>
-      </c>
-      <c r="D118" t="n">
-        <v>3868192.416318498</v>
-      </c>
-      <c r="E118" s="1" t="n">
-        <v>43951</v>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" t="inlineStr">
-        <is>
-          <t>LADDER_6Y_E057</t>
-        </is>
-      </c>
-      <c r="B119" t="n">
-        <v>6</v>
-      </c>
-      <c r="C119" t="n">
-        <v>57</v>
-      </c>
-      <c r="D119" t="n">
-        <v>3868192.416318498</v>
-      </c>
-      <c r="E119" s="1" t="n">
-        <v>43921</v>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" t="inlineStr">
-        <is>
-          <t>LADDER_6Y_E058</t>
-        </is>
-      </c>
-      <c r="B120" t="n">
-        <v>6</v>
-      </c>
-      <c r="C120" t="n">
-        <v>58</v>
-      </c>
-      <c r="D120" t="n">
-        <v>3868192.416318498</v>
-      </c>
-      <c r="E120" s="1" t="n">
-        <v>43890</v>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" t="inlineStr">
-        <is>
-          <t>LADDER_6Y_E059</t>
-        </is>
-      </c>
-      <c r="B121" t="n">
-        <v>6</v>
-      </c>
-      <c r="C121" t="n">
-        <v>59</v>
-      </c>
-      <c r="D121" t="n">
-        <v>3868192.416318498</v>
-      </c>
-      <c r="E121" s="1" t="n">
-        <v>43861</v>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" t="inlineStr">
-        <is>
-          <t>LADDER_6Y_E060</t>
-        </is>
-      </c>
-      <c r="B122" t="n">
-        <v>6</v>
-      </c>
-      <c r="C122" t="n">
-        <v>60</v>
-      </c>
-      <c r="D122" t="n">
-        <v>3868192.416318498</v>
-      </c>
-      <c r="E122" s="1" t="n">
-        <v>43830</v>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" t="inlineStr">
-        <is>
-          <t>LADDER_6Y_E061</t>
-        </is>
-      </c>
-      <c r="B123" t="n">
-        <v>6</v>
-      </c>
-      <c r="C123" t="n">
-        <v>61</v>
-      </c>
-      <c r="D123" t="n">
-        <v>3868192.416318498</v>
-      </c>
-      <c r="E123" s="1" t="n">
-        <v>43799</v>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" t="inlineStr">
-        <is>
-          <t>LADDER_6Y_E062</t>
-        </is>
-      </c>
-      <c r="B124" t="n">
-        <v>6</v>
-      </c>
-      <c r="C124" t="n">
-        <v>62</v>
-      </c>
-      <c r="D124" t="n">
-        <v>3868192.416318498</v>
-      </c>
-      <c r="E124" s="1" t="n">
-        <v>43769</v>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" t="inlineStr">
-        <is>
-          <t>LADDER_6Y_E063</t>
-        </is>
-      </c>
-      <c r="B125" t="n">
-        <v>6</v>
-      </c>
-      <c r="C125" t="n">
-        <v>63</v>
-      </c>
-      <c r="D125" t="n">
-        <v>3868192.416318498</v>
-      </c>
-      <c r="E125" s="1" t="n">
-        <v>43738</v>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" t="inlineStr">
-        <is>
-          <t>LADDER_6Y_E064</t>
-        </is>
-      </c>
-      <c r="B126" t="n">
-        <v>6</v>
-      </c>
-      <c r="C126" t="n">
-        <v>64</v>
-      </c>
-      <c r="D126" t="n">
-        <v>3868192.416318498</v>
-      </c>
-      <c r="E126" s="1" t="n">
-        <v>43708</v>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" t="inlineStr">
-        <is>
-          <t>LADDER_6Y_E065</t>
-        </is>
-      </c>
-      <c r="B127" t="n">
-        <v>6</v>
-      </c>
-      <c r="C127" t="n">
-        <v>65</v>
-      </c>
-      <c r="D127" t="n">
-        <v>3868192.416318498</v>
-      </c>
-      <c r="E127" s="1" t="n">
-        <v>43677</v>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" t="inlineStr">
-        <is>
-          <t>LADDER_6Y_E066</t>
-        </is>
-      </c>
-      <c r="B128" t="n">
-        <v>6</v>
-      </c>
-      <c r="C128" t="n">
-        <v>66</v>
-      </c>
-      <c r="D128" t="n">
-        <v>3868192.416318498</v>
-      </c>
-      <c r="E128" s="1" t="n">
-        <v>43646</v>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" t="inlineStr">
-        <is>
-          <t>LADDER_6Y_E067</t>
-        </is>
-      </c>
-      <c r="B129" t="n">
-        <v>6</v>
-      </c>
-      <c r="C129" t="n">
-        <v>67</v>
-      </c>
-      <c r="D129" t="n">
-        <v>3868192.416318498</v>
-      </c>
-      <c r="E129" s="1" t="n">
-        <v>43616</v>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" t="inlineStr">
-        <is>
-          <t>LADDER_6Y_E068</t>
-        </is>
-      </c>
-      <c r="B130" t="n">
-        <v>6</v>
-      </c>
-      <c r="C130" t="n">
-        <v>68</v>
-      </c>
-      <c r="D130" t="n">
-        <v>3868192.416318498</v>
-      </c>
-      <c r="E130" s="1" t="n">
-        <v>43585</v>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" t="inlineStr">
-        <is>
-          <t>LADDER_6Y_E069</t>
-        </is>
-      </c>
-      <c r="B131" t="n">
-        <v>6</v>
-      </c>
-      <c r="C131" t="n">
-        <v>69</v>
-      </c>
-      <c r="D131" t="n">
-        <v>3868192.416318498</v>
-      </c>
-      <c r="E131" s="1" t="n">
-        <v>43555</v>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" t="inlineStr">
-        <is>
-          <t>LADDER_6Y_E070</t>
-        </is>
-      </c>
-      <c r="B132" t="n">
-        <v>6</v>
-      </c>
-      <c r="C132" t="n">
-        <v>70</v>
-      </c>
-      <c r="D132" t="n">
-        <v>3868192.416318498</v>
-      </c>
-      <c r="E132" s="1" t="n">
-        <v>43524</v>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" t="inlineStr">
-        <is>
-          <t>LADDER_6Y_E071</t>
-        </is>
-      </c>
-      <c r="B133" t="n">
-        <v>6</v>
-      </c>
-      <c r="C133" t="n">
-        <v>71</v>
-      </c>
-      <c r="D133" t="n">
-        <v>3868192.416318498</v>
-      </c>
-      <c r="E133" s="1" t="n">
-        <v>43496</v>
+        <v>43676</v>
       </c>
     </row>
   </sheetData>
